--- a/backend/data/uploads/MES/2026-07-04_불량현황.xlsx
+++ b/backend/data/uploads/MES/2026-07-04_불량현황.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sihoo\PythonProject\TestProject\backend\data\uploads\MES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4ED21181-B230-4388-A110-CB74D352BFB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CF9EDCAD-CDB6-410F-904B-EBA9B45144A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-30828" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{67220551-A298-481C-900D-16BFF49FBC1F}"/>
+    <workbookView xWindow="-30828" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{171E3CDA-2146-4484-B0C4-BF9625F15CEE}"/>
   </bookViews>
   <sheets>
     <sheet name="불량현황" sheetId="1" r:id="rId1"/>
@@ -492,7 +492,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{599D6C3F-1611-4A7D-A85B-45DFEE27DE7F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE3463BD-7E62-40DA-BF69-45BDFB7D8554}">
   <dimension ref="B2:U12"/>
   <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
   <cols>

--- a/backend/data/uploads/MES/2026-07-04_불량현황.xlsx
+++ b/backend/data/uploads/MES/2026-07-04_불량현황.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sihoo\PythonProject\TestProject\backend\data\uploads\MES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CF9EDCAD-CDB6-410F-904B-EBA9B45144A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B5B46741-DD3F-4140-82DB-FEDC0DA9927D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-30828" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{171E3CDA-2146-4484-B0C4-BF9625F15CEE}"/>
+    <workbookView xWindow="-30828" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{335A633E-256A-4F4F-96A1-FE1C5B63E09A}"/>
   </bookViews>
   <sheets>
     <sheet name="불량현황" sheetId="1" r:id="rId1"/>
@@ -492,7 +492,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE3463BD-7E62-40DA-BF69-45BDFB7D8554}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05E15CF0-6A9E-4998-961B-4DCE0811E88B}">
   <dimension ref="B2:U12"/>
   <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
   <cols>

--- a/backend/data/uploads/MES/2026-07-04_불량현황.xlsx
+++ b/backend/data/uploads/MES/2026-07-04_불량현황.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sihoo\PythonProject\TestProject\backend\data\uploads\MES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B5B46741-DD3F-4140-82DB-FEDC0DA9927D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{320995C3-435B-446C-BDE7-CE50343066BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-30828" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{335A633E-256A-4F4F-96A1-FE1C5B63E09A}"/>
+    <workbookView xWindow="-30240" yWindow="8376" windowWidth="23040" windowHeight="12012" xr2:uid="{5983C157-D8BF-4982-A563-C492C41A84DD}"/>
   </bookViews>
   <sheets>
     <sheet name="불량현황" sheetId="1" r:id="rId1"/>
@@ -492,7 +492,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05E15CF0-6A9E-4998-961B-4DCE0811E88B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9CD2AD37-8727-47CC-8859-2F939572E1E3}">
   <dimension ref="B2:U12"/>
   <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
